--- a/docs/AI/Project_Tracker.xlsx
+++ b/docs/AI/Project_Tracker.xlsx
@@ -9963,7 +9963,7 @@
       <c r="K26" s="10"/>
       <c r="L26" s="10"/>
       <c r="M26" s="10" t="s">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="N26" s="10"/>
       <c r="O26" s="10" t="s">
@@ -9971,7 +9971,7 @@
       </c>
       <c r="P26" s="10" t="n">
         <f aca="false">IF(ISNUMBER(SEARCH("Done",M26)),1,IF(ISNUMBER(SEARCH("In Progress",M26)),0.5,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="66" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">

--- a/docs/AI/Project_Tracker.xlsx
+++ b/docs/AI/Project_Tracker.xlsx
@@ -4370,7 +4370,7 @@
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">SUMPRODUCT('Phase Tracker'!$E$2:$E$7,'Phase Tracker'!$D$2:$D$7)</f>
-        <v>0.1</v>
+        <v>0.28958333333333336</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>1</v>
@@ -4389,7 +4389,7 @@
         <v>19</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4421,7 +4421,7 @@
         <v>23</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="G9" s="7" t="n">
         <f aca="false">'Phase Tracker'!E3</f>
-        <v>0</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="I9" s="0" t="s">
         <v>25</v>
@@ -4445,7 +4445,7 @@
         <v>26</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>27</v>
+        <v>189</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
@@ -4461,7 +4461,7 @@
         <v>28</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4493,7 +4493,7 @@
         <v>30</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C12" s="5" t="n">
         <f aca="false">COUNTA(Milestones!$B$2:$B$25)</f>
@@ -4517,7 +4517,7 @@
         <v>31</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C13" s="5" t="n">
         <f aca="false">COUNTA(Epics!$C$2:C$100)</f>
@@ -4541,7 +4541,7 @@
         <v>32</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C14" s="5" t="n">
         <f aca="false">B15</f>
@@ -4590,7 +4590,7 @@
         <v>36</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>37</v>
+        <v>192</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="B21" s="6" t="n">
         <f aca="false">B7</f>
-        <v>0.1</v>
+        <v>0.28958333333333336</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>1</v>
@@ -5388,11 +5388,11 @@
       </c>
       <c r="E3" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$E$2:$E$200=A3)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$E$2:$E$200,A3),0)</f>
-        <v>0</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="F3" s="11" t="str">
         <f aca="false">IF(E3=1,"✅ Completed",IF(E3&gt;0,"🔄 In Progress","⏳ Planned"))</f>
-        <v>⏳ Planned</v>
+        <v>🔄 In Progress</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5661,11 +5661,11 @@
       <c r="I3" s="12"/>
       <c r="J3" s="15" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$D$2:$D$200=B3)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$D$2:$D$200,B3),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="12" t="str">
         <f aca="false">IF(COUNTIFS(Epics!$B$2:$B$100,B3,Epics!$K$2:$K$100,"*Blocked*")&gt;0,"🚫 Blocked",IF(J3=1,"✅ Completed",IF(J3&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>✅ Completed</v>
       </c>
       <c r="L3" s="12" t="n">
         <v>0</v>
@@ -5693,11 +5693,11 @@
       <c r="I4" s="12"/>
       <c r="J4" s="15" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$D$2:$D$200=B4)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$D$2:$D$200,B4),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="12" t="str">
         <f aca="false">IF(COUNTIFS(Epics!$B$2:$B$100,B4,Epics!$K$2:$K$100,"*Blocked*")&gt;0,"🚫 Blocked",IF(J4=1,"✅ Completed",IF(J4&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>✅ Completed</v>
       </c>
       <c r="L4" s="12" t="n">
         <v>0</v>
@@ -5725,11 +5725,11 @@
       <c r="I5" s="12"/>
       <c r="J5" s="15" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$D$2:$D$200=B5)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$D$2:$D$200,B5),0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K5" s="12" t="str">
         <f aca="false">IF(COUNTIFS(Epics!$B$2:$B$100,B5,Epics!$K$2:$K$100,"*Blocked*")&gt;0,"🚫 Blocked",IF(J5=1,"✅ Completed",IF(J5&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>🔄 In Progress</v>
       </c>
       <c r="L5" s="12" t="n">
         <v>0</v>
@@ -6456,11 +6456,11 @@
       <c r="I3" s="10"/>
       <c r="J3" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$C$2:$C$200=C3)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$C$2:$C$200,C3),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$C$2:$C$200,C3,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(J3=1,"✅ Completed",IF(J3&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>✅ Completed</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6485,11 +6485,11 @@
       <c r="I4" s="10"/>
       <c r="J4" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$C$2:$C$200=C4)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$C$2:$C$200,C4),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$C$2:$C$200,C4,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(J4=1,"✅ Completed",IF(J4&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>✅ Completed</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6514,11 +6514,11 @@
       <c r="I5" s="10"/>
       <c r="J5" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$C$2:$C$200=C5)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$C$2:$C$200,C5),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$C$2:$C$200,C5,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(J5=1,"✅ Completed",IF(J5&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>✅ Completed</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6543,11 +6543,11 @@
       <c r="I6" s="10"/>
       <c r="J6" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$C$2:$C$200=C6)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$C$2:$C$200,C6),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$C$2:$C$200,C6,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(J6=1,"✅ Completed",IF(J6&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>✅ Completed</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6572,11 +6572,11 @@
       <c r="I7" s="10"/>
       <c r="J7" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$C$2:$C$200=C7)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$C$2:$C$200,C7),0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K7" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$C$2:$C$200,C7,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(J7=1,"✅ Completed",IF(J7&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>🔄 In Progress</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7714,15 +7714,15 @@
       </c>
       <c r="H3" s="10" t="n">
         <f aca="false">SUMPRODUCT((Stories!$B$2:$B$200=A3)*(Stories!$P$2:$P$200))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I3" s="11" t="n">
         <f aca="false">IFERROR(H3/G3,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$B$2:$B$200,A3,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(I3=1,"✅ Completed",IF(I3&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>✅ Completed</v>
       </c>
       <c r="K3" s="10" t="s">
         <v>24</v>
@@ -7753,15 +7753,15 @@
       </c>
       <c r="H4" s="10" t="n">
         <f aca="false">SUMPRODUCT((Stories!$B$2:$B$200=A4)*(Stories!$P$2:$P$200))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" s="11" t="n">
         <f aca="false">IFERROR(H4/G4,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$B$2:$B$200,A4,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(I4=1,"✅ Completed",IF(I4&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>✅ Completed</v>
       </c>
       <c r="K4" s="10" t="s">
         <v>69</v>
@@ -7792,15 +7792,15 @@
       </c>
       <c r="H5" s="10" t="n">
         <f aca="false">SUMPRODUCT((Stories!$B$2:$B$200=A5)*(Stories!$P$2:$P$200))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="11" t="n">
         <f aca="false">IFERROR(H5/G5,0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J5" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$B$2:$B$200,A5,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(I5=1,"✅ Completed",IF(I5&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>🔄 In Progress</v>
       </c>
       <c r="K5" s="10" t="s">
         <v>72</v>
@@ -9748,7 +9748,7 @@
       <c r="K21" s="10"/>
       <c r="L21" s="10"/>
       <c r="M21" s="10" t="s">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="N21" s="10"/>
       <c r="O21" s="10" t="s">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="P21" s="10" t="n">
         <f aca="false">IF(ISNUMBER(SEARCH("Done",M21)),1,IF(ISNUMBER(SEARCH("In Progress",M21)),0.5,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9791,7 +9791,7 @@
       <c r="K22" s="10"/>
       <c r="L22" s="10"/>
       <c r="M22" s="10" t="s">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="N22" s="10"/>
       <c r="O22" s="10" t="s">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="P22" s="10" t="n">
         <f aca="false">IF(ISNUMBER(SEARCH("Done",M22)),1,IF(ISNUMBER(SEARCH("In Progress",M22)),0.5,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9834,7 +9834,7 @@
       <c r="K23" s="10"/>
       <c r="L23" s="10"/>
       <c r="M23" s="10" t="s">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="N23" s="10"/>
       <c r="O23" s="10" t="s">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="P23" s="10" t="n">
         <f aca="false">IF(ISNUMBER(SEARCH("Done",M23)),1,IF(ISNUMBER(SEARCH("In Progress",M23)),0.5,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="78.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9877,7 +9877,7 @@
       <c r="K24" s="10"/>
       <c r="L24" s="10"/>
       <c r="M24" s="10" t="s">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="N24" s="10"/>
       <c r="O24" s="10" t="s">
@@ -9885,7 +9885,7 @@
       </c>
       <c r="P24" s="10" t="n">
         <f aca="false">IF(ISNUMBER(SEARCH("Done",M24)),1,IF(ISNUMBER(SEARCH("In Progress",M24)),0.5,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="66" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9920,7 +9920,7 @@
       <c r="K25" s="10"/>
       <c r="L25" s="10"/>
       <c r="M25" s="10" t="s">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="N25" s="10"/>
       <c r="O25" s="10" t="s">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="P25" s="10" t="n">
         <f aca="false">IF(ISNUMBER(SEARCH("Done",M25)),1,IF(ISNUMBER(SEARCH("In Progress",M25)),0.5,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="78.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">

--- a/docs/AI/Project_Tracker.xlsx
+++ b/docs/AI/Project_Tracker.xlsx
@@ -4370,7 +4370,7 @@
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">SUMPRODUCT('Phase Tracker'!$E$2:$E$7,'Phase Tracker'!$D$2:$D$7)</f>
-        <v>0.28958333333333336</v>
+        <v>0.31666666666666665</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>1</v>
@@ -4389,7 +4389,7 @@
         <v>19</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4421,7 +4421,7 @@
         <v>23</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="G9" s="7" t="n">
         <f aca="false">'Phase Tracker'!E3</f>
-        <v>0.2916666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I9" s="0" t="s">
         <v>25</v>
@@ -4445,7 +4445,7 @@
         <v>26</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
@@ -4461,7 +4461,7 @@
         <v>28</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4493,7 +4493,7 @@
         <v>30</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12" s="5" t="n">
         <f aca="false">COUNTA(Milestones!$B$2:$B$25)</f>
@@ -4517,7 +4517,7 @@
         <v>31</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" s="5" t="n">
         <f aca="false">COUNTA(Epics!$C$2:C$100)</f>
@@ -4541,7 +4541,7 @@
         <v>32</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C14" s="5" t="n">
         <f aca="false">B15</f>
@@ -4590,7 +4590,7 @@
         <v>36</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="B21" s="6" t="n">
         <f aca="false">B7</f>
-        <v>0.28958333333333336</v>
+        <v>0.31666666666666665</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>1</v>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="E3" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$E$2:$E$200=A3)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$E$2:$E$200,A3),0)</f>
-        <v>0.2916666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F3" s="11" t="str">
         <f aca="false">IF(E3=1,"✅ Completed",IF(E3&gt;0,"🔄 In Progress","⏳ Planned"))</f>
@@ -5725,11 +5725,11 @@
       <c r="I5" s="12"/>
       <c r="J5" s="15" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$D$2:$D$200=B5)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$D$2:$D$200,B5),0)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K5" s="12" t="str">
         <f aca="false">IF(COUNTIFS(Epics!$B$2:$B$100,B5,Epics!$K$2:$K$100,"*Blocked*")&gt;0,"🚫 Blocked",IF(J5=1,"✅ Completed",IF(J5&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>🔄 In Progress</v>
+        <v>✅ Completed</v>
       </c>
       <c r="L5" s="12" t="n">
         <v>0</v>
@@ -6572,11 +6572,11 @@
       <c r="I7" s="10"/>
       <c r="J7" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$C$2:$C$200=C7)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$C$2:$C$200,C7),0)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K7" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$C$2:$C$200,C7,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(J7=1,"✅ Completed",IF(J7&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>🔄 In Progress</v>
+        <v>✅ Completed</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7792,15 +7792,15 @@
       </c>
       <c r="H5" s="10" t="n">
         <f aca="false">SUMPRODUCT((Stories!$B$2:$B$200=A5)*(Stories!$P$2:$P$200))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" s="11" t="n">
         <f aca="false">IFERROR(H5/G5,0)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J5" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$B$2:$B$200,A5,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(I5=1,"✅ Completed",IF(I5&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>🔄 In Progress</v>
+        <v>✅ Completed</v>
       </c>
       <c r="K5" s="10" t="s">
         <v>72</v>
@@ -10006,7 +10006,7 @@
       <c r="K27" s="10"/>
       <c r="L27" s="10"/>
       <c r="M27" s="10" t="s">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="N27" s="10"/>
       <c r="O27" s="10" t="s">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="P27" s="10" t="n">
         <f aca="false">IF(ISNUMBER(SEARCH("Done",M27)),1,IF(ISNUMBER(SEARCH("In Progress",M27)),0.5,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="78.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">

--- a/docs/AI/Project_Tracker.xlsx
+++ b/docs/AI/Project_Tracker.xlsx
@@ -4370,7 +4370,7 @@
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">SUMPRODUCT('Phase Tracker'!$E$2:$E$7,'Phase Tracker'!$D$2:$D$7)</f>
-        <v>0.31666666666666665</v>
+        <v>0.34375</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>1</v>
@@ -4389,7 +4389,7 @@
         <v>19</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4461,7 +4461,7 @@
         <v>28</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4517,7 +4517,7 @@
         <v>31</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13" s="5" t="n">
         <f aca="false">COUNTA(Epics!$C$2:C$100)</f>
@@ -4541,7 +4541,7 @@
         <v>32</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" s="5" t="n">
         <f aca="false">B15</f>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="B21" s="6" t="n">
         <f aca="false">B7</f>
-        <v>0.31666666666666665</v>
+        <v>0.34375</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>1</v>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="E3" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$E$2:$E$200=A3)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$E$2:$E$200,A3),0)</f>
-        <v>0.3333333333333333</v>
+        <v>0.375</v>
       </c>
       <c r="F3" s="11" t="str">
         <f aca="false">IF(E3=1,"✅ Completed",IF(E3&gt;0,"🔄 In Progress","⏳ Planned"))</f>
@@ -5757,11 +5757,11 @@
       <c r="I6" s="12"/>
       <c r="J6" s="15" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$D$2:$D$200=B6)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$D$2:$D$200,B6),0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K6" s="12" t="str">
         <f aca="false">IF(COUNTIFS(Epics!$B$2:$B$100,B6,Epics!$K$2:$K$100,"*Blocked*")&gt;0,"🚫 Blocked",IF(J6=1,"✅ Completed",IF(J6&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>🔄 In Progress</v>
       </c>
       <c r="L6" s="12" t="n">
         <v>0</v>
@@ -6601,11 +6601,11 @@
       <c r="I8" s="10"/>
       <c r="J8" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$C$2:$C$200=C8)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$C$2:$C$200,C8),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$C$2:$C$200,C8,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(J8=1,"✅ Completed",IF(J8&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>✅ Completed</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7831,15 +7831,15 @@
       </c>
       <c r="H6" s="10" t="n">
         <f aca="false">SUMPRODUCT((Stories!$B$2:$B$200=A6)*(Stories!$P$2:$P$200))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="11" t="n">
         <f aca="false">IFERROR(H6/G6,0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J6" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$B$2:$B$200,A6,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(I6=1,"✅ Completed",IF(I6&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>🔄 In Progress</v>
       </c>
       <c r="K6" s="10" t="s">
         <v>75</v>
@@ -10049,7 +10049,7 @@
       <c r="K28" s="10"/>
       <c r="L28" s="10"/>
       <c r="M28" s="10" t="s">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="N28" s="10"/>
       <c r="O28" s="10" t="s">
@@ -10057,7 +10057,7 @@
       </c>
       <c r="P28" s="10" t="n">
         <f aca="false">IF(ISNUMBER(SEARCH("Done",M28)),1,IF(ISNUMBER(SEARCH("In Progress",M28)),0.5,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="78.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">

--- a/docs/AI/Project_Tracker.xlsx
+++ b/docs/AI/Project_Tracker.xlsx
@@ -4370,7 +4370,7 @@
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">SUMPRODUCT('Phase Tracker'!$E$2:$E$7,'Phase Tracker'!$D$2:$D$7)</f>
-        <v>0.34375</v>
+        <v>0.37083333333333335</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>1</v>
@@ -4389,7 +4389,7 @@
         <v>19</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4421,7 +4421,7 @@
         <v>23</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -4445,7 +4445,7 @@
         <v>26</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
@@ -4461,7 +4461,7 @@
         <v>28</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4493,7 +4493,7 @@
         <v>30</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" s="5" t="n">
         <f aca="false">COUNTA(Milestones!$B$2:$B$25)</f>
@@ -4517,7 +4517,7 @@
         <v>31</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C13" s="5" t="n">
         <f aca="false">COUNTA(Epics!$C$2:C$100)</f>
@@ -4541,7 +4541,7 @@
         <v>32</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C14" s="5" t="n">
         <f aca="false">B15</f>
@@ -4590,7 +4590,7 @@
         <v>36</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="B21" s="6" t="n">
         <f aca="false">B7</f>
-        <v>0.34375</v>
+        <v>0.37083333333333335</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>1</v>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="E3" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$E$2:$E$200=A3)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$E$2:$E$200,A3),0)</f>
-        <v>0.375</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="F3" s="11" t="str">
         <f aca="false">IF(E3=1,"✅ Completed",IF(E3&gt;0,"🔄 In Progress","⏳ Planned"))</f>
@@ -5757,11 +5757,11 @@
       <c r="I6" s="12"/>
       <c r="J6" s="15" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$D$2:$D$200=B6)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$D$2:$D$200,B6),0)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K6" s="12" t="str">
         <f aca="false">IF(COUNTIFS(Epics!$B$2:$B$100,B6,Epics!$K$2:$K$100,"*Blocked*")&gt;0,"🚫 Blocked",IF(J6=1,"✅ Completed",IF(J6&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>🔄 In Progress</v>
+        <v>✅ Completed</v>
       </c>
       <c r="L6" s="12" t="n">
         <v>0</v>
@@ -6630,11 +6630,11 @@
       <c r="I9" s="10"/>
       <c r="J9" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$C$2:$C$200=C9)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$C$2:$C$200,C9),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$C$2:$C$200,C9,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(J9=1,"✅ Completed",IF(J9&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>✅ Completed</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7831,15 +7831,15 @@
       </c>
       <c r="H6" s="10" t="n">
         <f aca="false">SUMPRODUCT((Stories!$B$2:$B$200=A6)*(Stories!$P$2:$P$200))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" s="11" t="n">
         <f aca="false">IFERROR(H6/G6,0)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J6" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$B$2:$B$200,A6,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(I6=1,"✅ Completed",IF(I6&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>🔄 In Progress</v>
+        <v>✅ Completed</v>
       </c>
       <c r="K6" s="10" t="s">
         <v>75</v>
@@ -10092,7 +10092,7 @@
       <c r="K29" s="10"/>
       <c r="L29" s="10"/>
       <c r="M29" s="10" t="s">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="N29" s="10"/>
       <c r="O29" s="10" t="s">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="P29" s="10" t="n">
         <f aca="false">IF(ISNUMBER(SEARCH("Done",M29)),1,IF(ISNUMBER(SEARCH("In Progress",M29)),0.5,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="78.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">

--- a/docs/AI/Project_Tracker.xlsx
+++ b/docs/AI/Project_Tracker.xlsx
@@ -4370,7 +4370,7 @@
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">SUMPRODUCT('Phase Tracker'!$E$2:$E$7,'Phase Tracker'!$D$2:$D$7)</f>
-        <v>0.37083333333333335</v>
+        <v>0.425</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>1</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="G9" s="7" t="n">
         <f aca="false">'Phase Tracker'!E3</f>
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="I9" s="0" t="s">
         <v>25</v>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="E3" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$E$2:$E$200=A3)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$E$2:$E$200,A3),0)</f>
-        <v>0.4166666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="F3" s="11" t="str">
         <f aca="false">IF(E3=1,"✅ Completed",IF(E3&gt;0,"🔄 In Progress","⏳ Planned"))</f>
@@ -5789,11 +5789,11 @@
       <c r="I7" s="12"/>
       <c r="J7" s="15" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$D$2:$D$200=B7)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$D$2:$D$200,B7),0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K7" s="12" t="str">
         <f aca="false">IF(COUNTIFS(Epics!$B$2:$B$100,B7,Epics!$K$2:$K$100,"*Blocked*")&gt;0,"🚫 Blocked",IF(J7=1,"✅ Completed",IF(J7&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>🔄 In Progress</v>
       </c>
       <c r="L7" s="12" t="n">
         <v>0</v>
@@ -6659,11 +6659,11 @@
       <c r="I10" s="10"/>
       <c r="J10" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$C$2:$C$200=C10)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$C$2:$C$200,C10),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$C$2:$C$200,C10,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(J10=1,"✅ Completed",IF(J10&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>✅ Completed</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7870,15 +7870,15 @@
       </c>
       <c r="H7" s="10" t="n">
         <f aca="false">SUMPRODUCT((Stories!$B$2:$B$200=A7)*(Stories!$P$2:$P$200))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="11" t="n">
         <f aca="false">IFERROR(H7/G7,0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J7" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$B$2:$B$200,A7,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(I7=1,"✅ Completed",IF(I7&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>🔄 In Progress</v>
       </c>
       <c r="K7" s="10" t="s">
         <v>78</v>
@@ -10135,7 +10135,7 @@
       <c r="K30" s="10"/>
       <c r="L30" s="10"/>
       <c r="M30" s="10" t="s">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="N30" s="10"/>
       <c r="O30" s="10" t="s">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="P30" s="10" t="n">
         <f aca="false">IF(ISNUMBER(SEARCH("Done",M30)),1,IF(ISNUMBER(SEARCH("In Progress",M30)),0.5,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="66" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">

--- a/docs/AI/Project_Tracker.xlsx
+++ b/docs/AI/Project_Tracker.xlsx
@@ -4517,7 +4517,7 @@
         <v>31</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" s="5" t="n">
         <f aca="false">COUNTA(Epics!$C$2:C$100)</f>
@@ -4541,7 +4541,7 @@
         <v>32</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C14" s="5" t="n">
         <f aca="false">B15</f>

--- a/docs/AI/Project_Tracker.xlsx
+++ b/docs/AI/Project_Tracker.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1032" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="485">
   <si>
     <t xml:space="preserve">AI Marketplace — Project Dashboard</t>
   </si>
@@ -1745,6 +1745,38 @@
   </si>
   <si>
     <t xml:space="preserve">TOTAL SPEND (AED)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTG-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ML7-EP03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Category Domain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build and seed the real Category taxonomy domain, unblocking AI Conversation intake design.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build the real Category domain and seed the v1 launch taxonomy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As the engineering team, we need the real Category domain (category.categories, category.category_question_templates, and the real provider_categories join table) to exist and be seeded with the v1 launch taxonomy, so that AI-001's conversational intake has real categories and follow-up questions to resolve against instead of an interim workaround.
+This story builds the schema 04_DATABASE.md's Category Domain section already specifies and seeds it with the 14-category v1 launch taxonomy locked in docs/AI/17_CATEGORY_TAXONOMY.md (13_OPEN_DECISIONS.md item 1). It does not reconcile PRO-002's existing free-text provider_category_labels into the new real categories, and does not change how providers select categories today -- migrating provider-facing category selection to the real domain is a separate, future decision.
+Scope boundary: no AI conversation logic (that's AI-001/AI-002). No change to provider_category_labels or DIR-001's existing search matching.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Migration creates category.categories, category.category_question_templates, and category.provider_categories exactly per 04_DATABASE.md's Category Domain section (self-referential parent_category_id, JSONB options, composite PK on provider_categories).
+2. Migration seeds category.categories with the 14 categories from docs/AI/17_CATEGORY_TAXONOMY.md (slug, name, name_ar, sort_order).
+3. Migration seeds category.category_question_templates with every follow-up question listed in docs/AI/17_CATEGORY_TAXONOMY.md (question_text, question_text_ar, question_type, options, is_required, sort_order).
+4. Seed data is idempotent -- running the migration's upgrade twice, or an upgrade/downgrade/upgrade cycle, never creates duplicate category or question-template rows.
+5. A read-only service method (or endpoint, if warranted) exposes the seeded categories and their question templates so AI-001 can consume them once built.
+6. provider_category_labels and DIR-001's existing search query are completely unmodified -- this story adds a new, independent domain without changing provider-facing category behavior.
+7. Automated tests cover: migration upgrade/downgrade, seed data completeness (14 categories, correct per-category question counts), and idempotency.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIR-001, CTG-001</t>
   </si>
 </sst>
 </file>
@@ -4370,7 +4402,7 @@
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">SUMPRODUCT('Phase Tracker'!$E$2:$E$7,'Phase Tracker'!$D$2:$D$7)</f>
-        <v>0.425</v>
+        <v>0.4</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>1</v>
@@ -4431,7 +4463,7 @@
       </c>
       <c r="G9" s="7" t="n">
         <f aca="false">'Phase Tracker'!E3</f>
-        <v>0.5</v>
+        <v>0.46153846153846156</v>
       </c>
       <c r="I9" s="0" t="s">
         <v>25</v>
@@ -4521,7 +4553,7 @@
       </c>
       <c r="C13" s="5" t="n">
         <f aca="false">COUNTA(Epics!$C$2:C$100)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D13" s="5" t="str">
         <f aca="false">IF(B13=C13,"✅ Completed","🔄 In Progress")</f>
@@ -4545,7 +4577,7 @@
       </c>
       <c r="C14" s="5" t="n">
         <f aca="false">B15</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" s="5" t="str">
         <f aca="false">IF(B14=C14,"✅ Completed","🔄 In Progress")</f>
@@ -4558,7 +4590,7 @@
       </c>
       <c r="B15" s="5" t="n">
         <f aca="false">COUNTA(Stories!$A$2:A$200)</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
@@ -5388,7 +5420,7 @@
       </c>
       <c r="E3" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$E$2:$E$200=A3)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$E$2:$E$200,A3),0)</f>
-        <v>0.5</v>
+        <v>0.46153846153846156</v>
       </c>
       <c r="F3" s="11" t="str">
         <f aca="false">IF(E3=1,"✅ Completed",IF(E3&gt;0,"🔄 In Progress","⏳ Planned"))</f>
@@ -7044,17 +7076,33 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
+      <c r="A24" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>479</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>480</v>
+      </c>
       <c r="F24" s="10"/>
       <c r="G24" s="10"/>
       <c r="H24" s="10"/>
       <c r="I24" s="10"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
+      <c r="J24" s="11" t="n">
+        <f aca="false">IFERROR(SUMPRODUCT((Stories!$C$2:$C$200=C24)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$C$2:$C$200,C24),0)</f>
+        <v>0</v>
+      </c>
+      <c r="K24" s="11" t="str">
+        <f aca="false">IF(COUNTIFS(Stories!$C$2:$C$200,C24,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(J24=1,"✅ Completed",IF(J24&gt;0,"🔄 In Progress","⏳ Planned")))</f>
+        <v>⏳ Planned</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="10"/>
@@ -7905,7 +7953,7 @@
       <c r="F8" s="10"/>
       <c r="G8" s="10" t="n">
         <f aca="false">COUNTIF(Stories!$B$2:$B$200,A8)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" s="10" t="n">
         <f aca="false">SUMPRODUCT((Stories!$B$2:$B$200=A8)*(Stories!$P$2:$P$200))</f>
@@ -10225,7 +10273,7 @@
       </c>
       <c r="N32" s="10"/>
       <c r="O32" s="10" t="s">
-        <v>335</v>
+        <v>484</v>
       </c>
       <c r="P32" s="10" t="n">
         <f aca="false">IF(ISNUMBER(SEARCH("Done",M32)),1,IF(ISNUMBER(SEARCH("In Progress",M32)),0.5,0))</f>
@@ -10878,22 +10926,45 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="10"/>
-      <c r="B48" s="10"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="10"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
-      <c r="I48" s="10"/>
+      <c r="A48" s="10" t="s">
+        <v>477</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F48" s="10" t="s">
+        <v>481</v>
+      </c>
+      <c r="G48" s="10" t="s">
+        <v>482</v>
+      </c>
+      <c r="H48" s="10" t="s">
+        <v>483</v>
+      </c>
+      <c r="I48" s="10" t="s">
+        <v>295</v>
+      </c>
       <c r="J48" s="10"/>
       <c r="K48" s="10"/>
       <c r="L48" s="10"/>
-      <c r="M48" s="10"/>
+      <c r="M48" s="10" t="s">
+        <v>296</v>
+      </c>
       <c r="N48" s="10"/>
       <c r="O48" s="10"/>
-      <c r="P48" s="10"/>
+      <c r="P48" s="10" t="n">
+        <f aca="false">IF(ISNUMBER(SEARCH("Done",M48)),1,IF(ISNUMBER(SEARCH("In Progress",M48)),0.5,0))</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="10"/>

--- a/docs/AI/Project_Tracker.xlsx
+++ b/docs/AI/Project_Tracker.xlsx
@@ -4402,7 +4402,7 @@
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">SUMPRODUCT('Phase Tracker'!$E$2:$E$7,'Phase Tracker'!$D$2:$D$7)</f>
-        <v>0.4</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>1</v>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="G9" s="7" t="n">
         <f aca="false">'Phase Tracker'!E3</f>
-        <v>0.46153846153846156</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="I9" s="0" t="s">
         <v>25</v>
@@ -4549,7 +4549,7 @@
         <v>31</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" s="5" t="n">
         <f aca="false">COUNTA(Epics!$C$2:C$100)</f>
@@ -4573,7 +4573,7 @@
         <v>32</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14" s="5" t="n">
         <f aca="false">B15</f>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="E3" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$E$2:$E$200=A3)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$E$2:$E$200,A3),0)</f>
-        <v>0.46153846153846156</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="F3" s="11" t="str">
         <f aca="false">IF(E3=1,"✅ Completed",IF(E3&gt;0,"🔄 In Progress","⏳ Planned"))</f>
@@ -5853,11 +5853,11 @@
       <c r="I8" s="12"/>
       <c r="J8" s="15" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$D$2:$D$200=B8)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$D$2:$D$200,B8),0)</f>
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K8" s="12" t="str">
         <f aca="false">IF(COUNTIFS(Epics!$B$2:$B$100,B8,Epics!$K$2:$K$100,"*Blocked*")&gt;0,"🚫 Blocked",IF(J8=1,"✅ Completed",IF(J8&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>🔄 In Progress</v>
       </c>
       <c r="L8" s="12" t="n">
         <v>0</v>
@@ -7097,11 +7097,11 @@
       <c r="I24" s="10"/>
       <c r="J24" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$C$2:$C$200=C24)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$C$2:$C$200,C24),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$C$2:$C$200,C24,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(J24=1,"✅ Completed",IF(J24&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>✅ Completed</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7957,15 +7957,15 @@
       </c>
       <c r="H8" s="10" t="n">
         <f aca="false">SUMPRODUCT((Stories!$B$2:$B$200=A8)*(Stories!$P$2:$P$200))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="11" t="n">
         <f aca="false">IFERROR(H8/G8,0)</f>
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J8" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$B$2:$B$200,A8,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(I8=1,"✅ Completed",IF(I8&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>🔄 In Progress</v>
       </c>
       <c r="K8" s="10" t="s">
         <v>81</v>
@@ -10957,13 +10957,13 @@
       <c r="K48" s="10"/>
       <c r="L48" s="10"/>
       <c r="M48" s="10" t="s">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="N48" s="10"/>
       <c r="O48" s="10"/>
       <c r="P48" s="10" t="n">
         <f aca="false">IF(ISNUMBER(SEARCH("Done",M48)),1,IF(ISNUMBER(SEARCH("In Progress",M48)),0.5,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/docs/AI/Project_Tracker.xlsx
+++ b/docs/AI/Project_Tracker.xlsx
@@ -4402,7 +4402,7 @@
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">SUMPRODUCT('Phase Tracker'!$E$2:$E$7,'Phase Tracker'!$D$2:$D$7)</f>
-        <v>0.44999999999999996</v>
+        <v>0.5</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>1</v>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="G9" s="7" t="n">
         <f aca="false">'Phase Tracker'!E3</f>
-        <v>0.5384615384615384</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="I9" s="0" t="s">
         <v>25</v>
@@ -4525,7 +4525,7 @@
         <v>30</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12" s="5" t="n">
         <f aca="false">COUNTA(Milestones!$B$2:$B$25)</f>
@@ -4549,7 +4549,7 @@
         <v>31</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
         <f aca="false">COUNTA(Epics!$C$2:C$100)</f>
@@ -4573,7 +4573,7 @@
         <v>32</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C14" s="5" t="n">
         <f aca="false">B15</f>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="E3" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$E$2:$E$200=A3)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$E$2:$E$200,A3),0)</f>
-        <v>0.5384615384615384</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="F3" s="11" t="str">
         <f aca="false">IF(E3=1,"✅ Completed",IF(E3&gt;0,"🔄 In Progress","⏳ Planned"))</f>
@@ -5821,11 +5821,11 @@
       <c r="I7" s="12"/>
       <c r="J7" s="15" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$D$2:$D$200=B7)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$D$2:$D$200,B7),0)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K7" s="12" t="str">
         <f aca="false">IF(COUNTIFS(Epics!$B$2:$B$100,B7,Epics!$K$2:$K$100,"*Blocked*")&gt;0,"🚫 Blocked",IF(J7=1,"✅ Completed",IF(J7&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>🔄 In Progress</v>
+        <v>✅ Completed</v>
       </c>
       <c r="L7" s="12" t="n">
         <v>0</v>
@@ -6720,11 +6720,11 @@
       <c r="I11" s="10"/>
       <c r="J11" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$C$2:$C$200=C11)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$C$2:$C$200,C11),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$C$2:$C$200,C11,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(J11=1,"✅ Completed",IF(J11&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>✅ Completed</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7918,15 +7918,15 @@
       </c>
       <c r="H7" s="10" t="n">
         <f aca="false">SUMPRODUCT((Stories!$B$2:$B$200=A7)*(Stories!$P$2:$P$200))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" s="11" t="n">
         <f aca="false">IFERROR(H7/G7,0)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J7" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$B$2:$B$200,A7,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(I7=1,"✅ Completed",IF(I7&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>🔄 In Progress</v>
+        <v>✅ Completed</v>
       </c>
       <c r="K7" s="10" t="s">
         <v>78</v>
@@ -10226,7 +10226,7 @@
       <c r="K31" s="10"/>
       <c r="L31" s="10"/>
       <c r="M31" s="10" t="s">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="N31" s="10"/>
       <c r="O31" s="10" t="s">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="P31" s="10" t="n">
         <f aca="false">IF(ISNUMBER(SEARCH("Done",M31)),1,IF(ISNUMBER(SEARCH("In Progress",M31)),0.5,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="78.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">

--- a/docs/AI/Project_Tracker.xlsx
+++ b/docs/AI/Project_Tracker.xlsx
@@ -4402,7 +4402,7 @@
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">SUMPRODUCT('Phase Tracker'!$E$2:$E$7,'Phase Tracker'!$D$2:$D$7)</f>
-        <v>0.5</v>
+        <v>0.464</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>1</v>
@@ -4453,7 +4453,7 @@
         <v>23</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="G9" s="7" t="n">
         <f aca="false">'Phase Tracker'!E3</f>
-        <v>0.6153846153846154</v>
+        <v>0.56</v>
       </c>
       <c r="I9" s="0" t="s">
         <v>25</v>
@@ -4477,7 +4477,7 @@
         <v>26</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
@@ -4549,7 +4549,7 @@
         <v>31</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" s="5" t="n">
         <f aca="false">COUNTA(Epics!$C$2:C$100)</f>
@@ -4573,7 +4573,7 @@
         <v>32</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C14" s="5" t="n">
         <f aca="false">B15</f>
@@ -4622,7 +4622,7 @@
         <v>36</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="B21" s="6" t="n">
         <f aca="false">B7</f>
-        <v>0.37083333333333335</v>
+        <v>0.464</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>1</v>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="E3" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$E$2:$E$200=A3)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$E$2:$E$200,A3),0)</f>
-        <v>0.6153846153846154</v>
+        <v>0.56</v>
       </c>
       <c r="F3" s="11" t="str">
         <f aca="false">IF(E3=1,"✅ Completed",IF(E3&gt;0,"🔄 In Progress","⏳ Planned"))</f>
@@ -5853,7 +5853,7 @@
       <c r="I8" s="12"/>
       <c r="J8" s="15" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$D$2:$D$200=B8)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$D$2:$D$200,B8),0)</f>
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="K8" s="12" t="str">
         <f aca="false">IF(COUNTIFS(Epics!$B$2:$B$100,B8,Epics!$K$2:$K$100,"*Blocked*")&gt;0,"🚫 Blocked",IF(J8=1,"✅ Completed",IF(J8&gt;0,"🔄 In Progress","⏳ Planned")))</f>
@@ -6749,11 +6749,11 @@
       <c r="I12" s="10"/>
       <c r="J12" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$C$2:$C$200=C12)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$C$2:$C$200,C12),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$C$2:$C$200,C12,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(J12=1,"✅ Completed",IF(J12&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>✅ Completed</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7957,11 +7957,11 @@
       </c>
       <c r="H8" s="10" t="n">
         <f aca="false">SUMPRODUCT((Stories!$B$2:$B$200=A8)*(Stories!$P$2:$P$200))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" s="11" t="n">
         <f aca="false">IFERROR(H8/G8,0)</f>
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="J8" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$B$2:$B$200,A8,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(I8=1,"✅ Completed",IF(I8&gt;0,"🔄 In Progress","⏳ Planned")))</f>
@@ -10269,7 +10269,7 @@
       <c r="K32" s="10"/>
       <c r="L32" s="10"/>
       <c r="M32" s="10" t="s">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="N32" s="10"/>
       <c r="O32" s="10" t="s">

--- a/docs/AI/Project_Tracker.xlsx
+++ b/docs/AI/Project_Tracker.xlsx
@@ -4402,7 +4402,7 @@
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">SUMPRODUCT('Phase Tracker'!$E$2:$E$7,'Phase Tracker'!$D$2:$D$7)</f>
-        <v>0.464</v>
+        <v>0.49</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>1</v>
@@ -4453,7 +4453,7 @@
         <v>23</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="G9" s="7" t="n">
         <f aca="false">'Phase Tracker'!E3</f>
-        <v>0.56</v>
+        <v>0.6</v>
       </c>
       <c r="I9" s="0" t="s">
         <v>25</v>
@@ -4477,7 +4477,7 @@
         <v>26</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
@@ -4525,7 +4525,7 @@
         <v>30</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C12" s="5" t="n">
         <f aca="false">COUNTA(Milestones!$B$2:$B$25)</f>
@@ -4549,7 +4549,7 @@
         <v>31</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" s="5" t="n">
         <f aca="false">COUNTA(Epics!$C$2:C$100)</f>
@@ -4573,7 +4573,7 @@
         <v>32</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" s="5" t="n">
         <f aca="false">B15</f>
@@ -4622,7 +4622,7 @@
         <v>36</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="B21" s="6" t="n">
         <f aca="false">B7</f>
-        <v>0.464</v>
+        <v>0.49</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>1</v>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="E3" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$E$2:$E$200=A3)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$E$2:$E$200,A3),0)</f>
-        <v>0.56</v>
+        <v>0.6</v>
       </c>
       <c r="F3" s="11" t="str">
         <f aca="false">IF(E3=1,"✅ Completed",IF(E3&gt;0,"🔄 In Progress","⏳ Planned"))</f>
@@ -5853,11 +5853,11 @@
       <c r="I8" s="12"/>
       <c r="J8" s="15" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$D$2:$D$200=B8)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$D$2:$D$200,B8),0)</f>
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="K8" s="12" t="str">
         <f aca="false">IF(COUNTIFS(Epics!$B$2:$B$100,B8,Epics!$K$2:$K$100,"*Blocked*")&gt;0,"🚫 Blocked",IF(J8=1,"✅ Completed",IF(J8&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>🔄 In Progress</v>
+        <v>✅ Completed</v>
       </c>
       <c r="L8" s="12" t="n">
         <v>0</v>
@@ -6778,11 +6778,11 @@
       <c r="I13" s="10"/>
       <c r="J13" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$C$2:$C$200=C13)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$C$2:$C$200,C13),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$C$2:$C$200,C13,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(J13=1,"✅ Completed",IF(J13&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>✅ Completed</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7957,15 +7957,15 @@
       </c>
       <c r="H8" s="10" t="n">
         <f aca="false">SUMPRODUCT((Stories!$B$2:$B$200=A8)*(Stories!$P$2:$P$200))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I8" s="11" t="n">
         <f aca="false">IFERROR(H8/G8,0)</f>
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="J8" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$B$2:$B$200,A8,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(I8=1,"✅ Completed",IF(I8&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>🔄 In Progress</v>
+        <v>✅ Completed</v>
       </c>
       <c r="K8" s="10" t="s">
         <v>81</v>
@@ -10312,7 +10312,7 @@
       <c r="K33" s="10"/>
       <c r="L33" s="10"/>
       <c r="M33" s="10" t="s">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="N33" s="10"/>
       <c r="O33" s="10" t="s">

--- a/docs/AI/Project_Tracker.xlsx
+++ b/docs/AI/Project_Tracker.xlsx
@@ -4402,7 +4402,7 @@
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">SUMPRODUCT('Phase Tracker'!$E$2:$E$7,'Phase Tracker'!$D$2:$D$7)</f>
-        <v>0.49</v>
+        <v>0.516</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>1</v>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="G9" s="7" t="n">
         <f aca="false">'Phase Tracker'!E3</f>
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="I9" s="0" t="s">
         <v>25</v>
@@ -4549,7 +4549,7 @@
         <v>31</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" s="5" t="n">
         <f aca="false">COUNTA(Epics!$C$2:C$100)</f>
@@ -4573,7 +4573,7 @@
         <v>32</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C14" s="5" t="n">
         <f aca="false">B15</f>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="B21" s="6" t="n">
         <f aca="false">B7</f>
-        <v>0.49</v>
+        <v>0.516</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>1</v>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="E3" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$E$2:$E$200=A3)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$E$2:$E$200,A3),0)</f>
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="F3" s="11" t="str">
         <f aca="false">IF(E3=1,"✅ Completed",IF(E3&gt;0,"🔄 In Progress","⏳ Planned"))</f>
@@ -5885,11 +5885,11 @@
       <c r="I9" s="12"/>
       <c r="J9" s="15" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$D$2:$D$200=B9)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$D$2:$D$200,B9),0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K9" s="12" t="str">
         <f aca="false">IF(COUNTIFS(Epics!$B$2:$B$100,B9,Epics!$K$2:$K$100,"*Blocked*")&gt;0,"🚫 Blocked",IF(J9=1,"✅ Completed",IF(J9&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>🔄 In Progress</v>
       </c>
       <c r="L9" s="12" t="n">
         <v>0</v>
@@ -6807,11 +6807,11 @@
       <c r="I14" s="10"/>
       <c r="J14" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$C$2:$C$200=C14)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$C$2:$C$200,C14),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$C$2:$C$200,C14,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(J14=1,"✅ Completed",IF(J14&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>✅ Completed</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7996,15 +7996,15 @@
       </c>
       <c r="H9" s="10" t="n">
         <f aca="false">SUMPRODUCT((Stories!$B$2:$B$200=A9)*(Stories!$P$2:$P$200))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="11" t="n">
         <f aca="false">IFERROR(H9/G9,0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J9" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$B$2:$B$200,A9,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(I9=1,"✅ Completed",IF(I9&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>🔄 In Progress</v>
       </c>
       <c r="K9" s="10" t="s">
         <v>84</v>
@@ -10355,7 +10355,7 @@
       <c r="K34" s="10"/>
       <c r="L34" s="10"/>
       <c r="M34" s="10" t="s">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="N34" s="10"/>
       <c r="O34" s="10" t="s">

--- a/docs/AI/Project_Tracker.xlsx
+++ b/docs/AI/Project_Tracker.xlsx
@@ -4402,7 +4402,7 @@
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">SUMPRODUCT('Phase Tracker'!$E$2:$E$7,'Phase Tracker'!$D$2:$D$7)</f>
-        <v>0.516</v>
+        <v>0.542</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>1</v>
@@ -4453,7 +4453,7 @@
         <v>23</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="G9" s="7" t="n">
         <f aca="false">'Phase Tracker'!E3</f>
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="I9" s="0" t="s">
         <v>25</v>
@@ -4477,7 +4477,7 @@
         <v>26</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
@@ -4525,7 +4525,7 @@
         <v>30</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C12" s="5" t="n">
         <f aca="false">COUNTA(Milestones!$B$2:$B$25)</f>
@@ -4549,7 +4549,7 @@
         <v>31</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" s="5" t="n">
         <f aca="false">COUNTA(Epics!$C$2:C$100)</f>
@@ -4573,7 +4573,7 @@
         <v>32</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C14" s="5" t="n">
         <f aca="false">B15</f>
@@ -4622,7 +4622,7 @@
         <v>36</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="B21" s="6" t="n">
         <f aca="false">B7</f>
-        <v>0.516</v>
+        <v>0.542</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>1</v>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="E3" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$E$2:$E$200=A3)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$E$2:$E$200,A3),0)</f>
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="F3" s="11" t="str">
         <f aca="false">IF(E3=1,"✅ Completed",IF(E3&gt;0,"🔄 In Progress","⏳ Planned"))</f>
@@ -5885,11 +5885,11 @@
       <c r="I9" s="12"/>
       <c r="J9" s="15" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$D$2:$D$200=B9)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$D$2:$D$200,B9),0)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K9" s="12" t="str">
         <f aca="false">IF(COUNTIFS(Epics!$B$2:$B$100,B9,Epics!$K$2:$K$100,"*Blocked*")&gt;0,"🚫 Blocked",IF(J9=1,"✅ Completed",IF(J9&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>🔄 In Progress</v>
+        <v>✅ Completed</v>
       </c>
       <c r="L9" s="12" t="n">
         <v>0</v>
@@ -6836,11 +6836,11 @@
       <c r="I15" s="10"/>
       <c r="J15" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$C$2:$C$200=C15)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$C$2:$C$200,C15),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$C$2:$C$200,C15,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(J15=1,"✅ Completed",IF(J15&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>✅ Completed</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7996,15 +7996,15 @@
       </c>
       <c r="H9" s="10" t="n">
         <f aca="false">SUMPRODUCT((Stories!$B$2:$B$200=A9)*(Stories!$P$2:$P$200))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" s="11" t="n">
         <f aca="false">IFERROR(H9/G9,0)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J9" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$B$2:$B$200,A9,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(I9=1,"✅ Completed",IF(I9&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>🔄 In Progress</v>
+        <v>✅ Completed</v>
       </c>
       <c r="K9" s="10" t="s">
         <v>84</v>
@@ -10398,7 +10398,7 @@
       <c r="K35" s="10"/>
       <c r="L35" s="10"/>
       <c r="M35" s="10" t="s">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="N35" s="10"/>
       <c r="O35" s="10" t="s">
